--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/VFOutpatMedReq</t>
+    <t>http://va.gov/fhir/ConceptMap/CMVFOutpatMedReq</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFOutpatMedReq</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFOutpatMedReq</t>
   </si>
   <si>
     <t>Display</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOutpatMedReq.xlsx
+++ b/docs/CMVFOutpatMedReq.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
